--- a/dev/epa_monitoring_data_K_2024-05-27_to_2025-05-26.xlsx
+++ b/dev/epa_monitoring_data_K_2024-05-27_to_2025-05-26.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H656"/>
+  <dimension ref="A1:H658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
@@ -455,6 +455,9 @@
           <t>per cent by volume</t>
         </is>
       </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
       <c r="E2">
         <v>712</v>
       </c>
@@ -3094,6 +3097,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
       <c r="E93">
         <v>2</v>
       </c>
@@ -3384,6 +3390,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
       <c r="E103">
         <v>2</v>
       </c>
@@ -3703,6 +3712,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D114">
+        <v>4</v>
+      </c>
       <c r="E114">
         <v>4</v>
       </c>
@@ -3732,6 +3744,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D115">
+        <v>4</v>
+      </c>
       <c r="E115">
         <v>2</v>
       </c>
@@ -3848,6 +3863,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D119">
+        <v>4</v>
+      </c>
       <c r="E119">
         <v>2</v>
       </c>
@@ -3877,6 +3895,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D120">
+        <v>4</v>
+      </c>
       <c r="E120">
         <v>2</v>
       </c>
@@ -4370,6 +4391,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D137">
+        <v>4</v>
+      </c>
       <c r="E137">
         <v>9</v>
       </c>
@@ -4660,6 +4684,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D147">
+        <v>4</v>
+      </c>
       <c r="E147">
         <v>9</v>
       </c>
@@ -4979,6 +5006,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D158">
+        <v>4</v>
+      </c>
       <c r="E158">
         <v>10</v>
       </c>
@@ -5037,6 +5067,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D160">
+        <v>4</v>
+      </c>
       <c r="E160">
         <v>9</v>
       </c>
@@ -5153,6 +5186,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D164">
+        <v>4</v>
+      </c>
       <c r="E164">
         <v>9</v>
       </c>
@@ -5182,6 +5218,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D165">
+        <v>4</v>
+      </c>
       <c r="E165">
         <v>9</v>
       </c>
@@ -5675,6 +5714,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D182">
+        <v>4</v>
+      </c>
       <c r="E182">
         <v>7</v>
       </c>
@@ -5965,6 +6007,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D192">
+        <v>4</v>
+      </c>
       <c r="E192">
         <v>7</v>
       </c>
@@ -6284,6 +6329,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D203">
+        <v>4</v>
+      </c>
       <c r="E203">
         <v>7</v>
       </c>
@@ -6342,6 +6390,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D205">
+        <v>4</v>
+      </c>
       <c r="E205">
         <v>7</v>
       </c>
@@ -6458,6 +6509,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D209">
+        <v>4</v>
+      </c>
       <c r="E209">
         <v>7</v>
       </c>
@@ -6487,6 +6541,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D210">
+        <v>4</v>
+      </c>
       <c r="E210">
         <v>7</v>
       </c>
@@ -6980,6 +7037,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D227">
+        <v>4</v>
+      </c>
       <c r="E227">
         <v>4</v>
       </c>
@@ -7212,6 +7272,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D235">
+        <v>4</v>
+      </c>
       <c r="E235">
         <v>4</v>
       </c>
@@ -7502,6 +7565,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D245">
+        <v>4</v>
+      </c>
       <c r="E245">
         <v>4</v>
       </c>
@@ -7560,6 +7626,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D247">
+        <v>4</v>
+      </c>
       <c r="E247">
         <v>4</v>
       </c>
@@ -7647,6 +7716,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D250">
+        <v>4</v>
+      </c>
       <c r="E250">
         <v>4</v>
       </c>
@@ -7676,6 +7748,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D251">
+        <v>4</v>
+      </c>
       <c r="E251">
         <v>4</v>
       </c>
@@ -7792,6 +7867,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
       <c r="E255">
         <v>9</v>
       </c>
@@ -7908,6 +7986,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D259">
+        <v>4</v>
+      </c>
       <c r="E259">
         <v>9</v>
       </c>
@@ -8053,6 +8134,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D264">
+        <v>4</v>
+      </c>
       <c r="E264">
         <v>10</v>
       </c>
@@ -8111,6 +8195,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D266">
+        <v>4</v>
+      </c>
       <c r="E266">
         <v>9</v>
       </c>
@@ -8198,6 +8285,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D269">
+        <v>4</v>
+      </c>
       <c r="E269">
         <v>9</v>
       </c>
@@ -8227,6 +8317,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D270">
+        <v>4</v>
+      </c>
       <c r="E270">
         <v>9</v>
       </c>
@@ -8314,6 +8407,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D273">
+        <v>4</v>
+      </c>
       <c r="E273">
         <v>1</v>
       </c>
@@ -8546,6 +8642,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D281">
+        <v>4</v>
+      </c>
       <c r="E281">
         <v>1</v>
       </c>
@@ -8836,6 +8935,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D291">
+        <v>4</v>
+      </c>
       <c r="E291">
         <v>1</v>
       </c>
@@ -8865,6 +8967,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D292">
+        <v>4</v>
+      </c>
       <c r="E292">
         <v>1</v>
       </c>
@@ -8952,6 +9057,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D295">
+        <v>4</v>
+      </c>
       <c r="E295">
         <v>1</v>
       </c>
@@ -8981,6 +9089,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D296">
+        <v>4</v>
+      </c>
       <c r="E296">
         <v>1</v>
       </c>
@@ -9242,6 +9353,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D305">
+        <v>4</v>
+      </c>
       <c r="E305">
         <v>9</v>
       </c>
@@ -9590,6 +9704,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D317">
+        <v>4</v>
+      </c>
       <c r="E317">
         <v>9</v>
       </c>
@@ -10402,6 +10519,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D345">
+        <v>4</v>
+      </c>
       <c r="E345">
         <v>10</v>
       </c>
@@ -10489,6 +10609,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D348">
+        <v>4</v>
+      </c>
       <c r="E348">
         <v>9</v>
       </c>
@@ -10605,6 +10728,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D352">
+        <v>4</v>
+      </c>
       <c r="E352">
         <v>9</v>
       </c>
@@ -10634,6 +10760,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D353">
+        <v>4</v>
+      </c>
       <c r="E353">
         <v>9</v>
       </c>
@@ -11098,6 +11227,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D369">
+        <v>4</v>
+      </c>
       <c r="E369">
         <v>3</v>
       </c>
@@ -11127,6 +11259,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D370">
+        <v>4</v>
+      </c>
       <c r="E370">
         <v>3</v>
       </c>
@@ -11156,6 +11291,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D371">
+        <v>1</v>
+      </c>
       <c r="E371">
         <v>3</v>
       </c>
@@ -11185,6 +11323,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D372">
+        <v>1</v>
+      </c>
       <c r="E372">
         <v>3</v>
       </c>
@@ -11214,6 +11355,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D373">
+        <v>1</v>
+      </c>
       <c r="E373">
         <v>1</v>
       </c>
@@ -11243,6 +11387,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D374">
+        <v>1</v>
+      </c>
       <c r="E374">
         <v>3</v>
       </c>
@@ -11272,6 +11419,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D375">
+        <v>4</v>
+      </c>
       <c r="E375">
         <v>3</v>
       </c>
@@ -11301,6 +11451,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D376">
+        <v>4</v>
+      </c>
       <c r="E376">
         <v>3</v>
       </c>
@@ -11330,6 +11483,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D377">
+        <v>1</v>
+      </c>
       <c r="E377">
         <v>3</v>
       </c>
@@ -11359,6 +11515,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D378">
+        <v>1</v>
+      </c>
       <c r="E378">
         <v>3</v>
       </c>
@@ -11388,6 +11547,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D379">
+        <v>4</v>
+      </c>
       <c r="E379">
         <v>3</v>
       </c>
@@ -11417,6 +11579,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D380">
+        <v>1</v>
+      </c>
       <c r="E380">
         <v>3</v>
       </c>
@@ -11446,6 +11611,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D381">
+        <v>1</v>
+      </c>
       <c r="E381">
         <v>1</v>
       </c>
@@ -11475,6 +11643,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D382">
+        <v>4</v>
+      </c>
       <c r="E382">
         <v>3</v>
       </c>
@@ -11504,6 +11675,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D383">
+        <v>1</v>
+      </c>
       <c r="E383">
         <v>3</v>
       </c>
@@ -11533,6 +11707,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D384">
+        <v>4</v>
+      </c>
       <c r="E384">
         <v>3</v>
       </c>
@@ -11562,6 +11739,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D385">
+        <v>1</v>
+      </c>
       <c r="E385">
         <v>3</v>
       </c>
@@ -11591,6 +11771,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
       <c r="E386">
         <v>3</v>
       </c>
@@ -11620,6 +11803,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D387">
+        <v>1</v>
+      </c>
       <c r="E387">
         <v>3</v>
       </c>
@@ -11649,6 +11835,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D388">
+        <v>4</v>
+      </c>
       <c r="E388">
         <v>3</v>
       </c>
@@ -11678,6 +11867,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
       <c r="E389">
         <v>3</v>
       </c>
@@ -11707,6 +11899,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D390">
+        <v>4</v>
+      </c>
       <c r="E390">
         <v>4</v>
       </c>
@@ -11736,6 +11931,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D391">
+        <v>4</v>
+      </c>
       <c r="E391">
         <v>3</v>
       </c>
@@ -11765,6 +11963,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D392">
+        <v>4</v>
+      </c>
       <c r="E392">
         <v>3</v>
       </c>
@@ -11794,6 +11995,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D393">
+        <v>4</v>
+      </c>
       <c r="E393">
         <v>2</v>
       </c>
@@ -11823,6 +12027,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D394">
+        <v>4</v>
+      </c>
       <c r="E394">
         <v>3</v>
       </c>
@@ -11852,6 +12059,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D395">
+        <v>1</v>
+      </c>
       <c r="E395">
         <v>1</v>
       </c>
@@ -11881,6 +12091,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D396">
+        <v>4</v>
+      </c>
       <c r="E396">
         <v>3</v>
       </c>
@@ -11910,6 +12123,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D397">
+        <v>4</v>
+      </c>
       <c r="E397">
         <v>3</v>
       </c>
@@ -11939,6 +12155,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D398">
+        <v>1</v>
+      </c>
       <c r="E398">
         <v>1</v>
       </c>
@@ -11968,6 +12187,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D399">
+        <v>1</v>
+      </c>
       <c r="E399">
         <v>1</v>
       </c>
@@ -11997,6 +12219,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D400">
+        <v>1</v>
+      </c>
       <c r="E400">
         <v>1</v>
       </c>
@@ -12026,6 +12251,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D401">
+        <v>1</v>
+      </c>
       <c r="E401">
         <v>1</v>
       </c>
@@ -12055,6 +12283,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D402">
+        <v>1</v>
+      </c>
       <c r="E402">
         <v>1</v>
       </c>
@@ -12084,6 +12315,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D403">
+        <v>1</v>
+      </c>
       <c r="E403">
         <v>1</v>
       </c>
@@ -12113,6 +12347,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D404">
+        <v>1</v>
+      </c>
       <c r="E404">
         <v>1</v>
       </c>
@@ -12142,6 +12379,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D405">
+        <v>1</v>
+      </c>
       <c r="E405">
         <v>1</v>
       </c>
@@ -12171,6 +12411,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D406">
+        <v>1</v>
+      </c>
       <c r="E406">
         <v>1</v>
       </c>
@@ -12200,6 +12443,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D407">
+        <v>1</v>
+      </c>
       <c r="E407">
         <v>1</v>
       </c>
@@ -12229,6 +12475,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D408">
+        <v>1</v>
+      </c>
       <c r="E408">
         <v>1</v>
       </c>
@@ -12258,6 +12507,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D409">
+        <v>1</v>
+      </c>
       <c r="E409">
         <v>1</v>
       </c>
@@ -12287,6 +12539,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D410">
+        <v>1</v>
+      </c>
       <c r="E410">
         <v>1</v>
       </c>
@@ -12316,6 +12571,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D411">
+        <v>1</v>
+      </c>
       <c r="E411">
         <v>3</v>
       </c>
@@ -12345,6 +12603,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D412">
+        <v>4</v>
+      </c>
       <c r="E412">
         <v>1</v>
       </c>
@@ -12374,6 +12635,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D413">
+        <v>4</v>
+      </c>
       <c r="E413">
         <v>1</v>
       </c>
@@ -12403,6 +12667,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D414">
+        <v>1</v>
+      </c>
       <c r="E414">
         <v>1</v>
       </c>
@@ -12432,6 +12699,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D415">
+        <v>1</v>
+      </c>
       <c r="E415">
         <v>1</v>
       </c>
@@ -12461,6 +12731,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D416">
+        <v>1</v>
+      </c>
       <c r="E416">
         <v>1</v>
       </c>
@@ -12490,6 +12763,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D417">
+        <v>4</v>
+      </c>
       <c r="E417">
         <v>1</v>
       </c>
@@ -12519,6 +12795,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D418">
+        <v>4</v>
+      </c>
       <c r="E418">
         <v>1</v>
       </c>
@@ -12548,6 +12827,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D419">
+        <v>1</v>
+      </c>
       <c r="E419">
         <v>1</v>
       </c>
@@ -12577,6 +12859,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D420">
+        <v>1</v>
+      </c>
       <c r="E420">
         <v>1</v>
       </c>
@@ -12606,6 +12891,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D421">
+        <v>4</v>
+      </c>
       <c r="E421">
         <v>1</v>
       </c>
@@ -12635,6 +12923,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D422">
+        <v>1</v>
+      </c>
       <c r="E422">
         <v>1</v>
       </c>
@@ -12664,6 +12955,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D423">
+        <v>4</v>
+      </c>
       <c r="E423">
         <v>1</v>
       </c>
@@ -12693,6 +12987,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D424">
+        <v>1</v>
+      </c>
       <c r="E424">
         <v>1</v>
       </c>
@@ -12722,6 +13019,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D425">
+        <v>4</v>
+      </c>
       <c r="E425">
         <v>1</v>
       </c>
@@ -12751,6 +13051,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D426">
+        <v>1</v>
+      </c>
       <c r="E426">
         <v>1</v>
       </c>
@@ -12780,6 +13083,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D427">
+        <v>1</v>
+      </c>
       <c r="E427">
         <v>1</v>
       </c>
@@ -12809,6 +13115,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D428">
+        <v>1</v>
+      </c>
       <c r="E428">
         <v>1</v>
       </c>
@@ -12838,6 +13147,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D429">
+        <v>4</v>
+      </c>
       <c r="E429">
         <v>1</v>
       </c>
@@ -12867,6 +13179,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D430">
+        <v>4</v>
+      </c>
       <c r="E430">
         <v>1</v>
       </c>
@@ -12896,6 +13211,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D431">
+        <v>4</v>
+      </c>
       <c r="E431">
         <v>2</v>
       </c>
@@ -12925,6 +13243,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D432">
+        <v>4</v>
+      </c>
       <c r="E432">
         <v>1</v>
       </c>
@@ -12954,6 +13275,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D433">
+        <v>4</v>
+      </c>
       <c r="E433">
         <v>1</v>
       </c>
@@ -12983,6 +13307,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D434">
+        <v>4</v>
+      </c>
       <c r="E434">
         <v>2</v>
       </c>
@@ -13012,6 +13339,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D435">
+        <v>4</v>
+      </c>
       <c r="E435">
         <v>1</v>
       </c>
@@ -13041,6 +13371,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D436">
+        <v>4</v>
+      </c>
       <c r="E436">
         <v>1</v>
       </c>
@@ -13070,6 +13403,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D437">
+        <v>4</v>
+      </c>
       <c r="E437">
         <v>1</v>
       </c>
@@ -13099,6 +13435,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D438">
+        <v>1</v>
+      </c>
       <c r="E438">
         <v>1</v>
       </c>
@@ -13128,6 +13467,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D439">
+        <v>1</v>
+      </c>
       <c r="E439">
         <v>1</v>
       </c>
@@ -13157,6 +13499,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D440">
+        <v>1</v>
+      </c>
       <c r="E440">
         <v>1</v>
       </c>
@@ -13186,6 +13531,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D441">
+        <v>1</v>
+      </c>
       <c r="E441">
         <v>1</v>
       </c>
@@ -13215,6 +13563,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D442">
+        <v>1</v>
+      </c>
       <c r="E442">
         <v>1</v>
       </c>
@@ -13244,6 +13595,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D443">
+        <v>4</v>
+      </c>
       <c r="E443">
         <v>2</v>
       </c>
@@ -13273,6 +13627,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D444">
+        <v>1</v>
+      </c>
       <c r="E444">
         <v>1</v>
       </c>
@@ -13302,6 +13659,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D445">
+        <v>1</v>
+      </c>
       <c r="E445">
         <v>1</v>
       </c>
@@ -13331,6 +13691,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D446">
+        <v>4</v>
+      </c>
       <c r="E446">
         <v>2</v>
       </c>
@@ -13360,6 +13723,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D447">
+        <v>1</v>
+      </c>
       <c r="E447">
         <v>2</v>
       </c>
@@ -13389,6 +13755,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D448">
+        <v>1</v>
+      </c>
       <c r="E448">
         <v>2</v>
       </c>
@@ -13418,6 +13787,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D449">
+        <v>1</v>
+      </c>
       <c r="E449">
         <v>1</v>
       </c>
@@ -13447,6 +13819,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D450">
+        <v>1</v>
+      </c>
       <c r="E450">
         <v>1</v>
       </c>
@@ -13476,6 +13851,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D451">
+        <v>1</v>
+      </c>
       <c r="E451">
         <v>2</v>
       </c>
@@ -13505,6 +13883,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D452">
+        <v>4</v>
+      </c>
       <c r="E452">
         <v>2</v>
       </c>
@@ -13534,6 +13915,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D453">
+        <v>4</v>
+      </c>
       <c r="E453">
         <v>2</v>
       </c>
@@ -13563,6 +13947,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D454">
+        <v>1</v>
+      </c>
       <c r="E454">
         <v>1</v>
       </c>
@@ -13592,6 +13979,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D455">
+        <v>1</v>
+      </c>
       <c r="E455">
         <v>1</v>
       </c>
@@ -13621,6 +14011,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D456">
+        <v>1</v>
+      </c>
       <c r="E456">
         <v>2</v>
       </c>
@@ -13650,6 +14043,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D457">
+        <v>1</v>
+      </c>
       <c r="E457">
         <v>2</v>
       </c>
@@ -13679,6 +14075,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D458">
+        <v>4</v>
+      </c>
       <c r="E458">
         <v>2</v>
       </c>
@@ -13708,6 +14107,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D459">
+        <v>1</v>
+      </c>
       <c r="E459">
         <v>2</v>
       </c>
@@ -13737,6 +14139,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D460">
+        <v>1</v>
+      </c>
       <c r="E460">
         <v>1</v>
       </c>
@@ -13766,6 +14171,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D461">
+        <v>1</v>
+      </c>
       <c r="E461">
         <v>1</v>
       </c>
@@ -13795,6 +14203,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D462">
+        <v>1</v>
+      </c>
       <c r="E462">
         <v>1</v>
       </c>
@@ -13824,6 +14235,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D463">
+        <v>1</v>
+      </c>
       <c r="E463">
         <v>1</v>
       </c>
@@ -13853,6 +14267,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D464">
+        <v>1</v>
+      </c>
       <c r="E464">
         <v>1</v>
       </c>
@@ -13882,6 +14299,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D465">
+        <v>1</v>
+      </c>
       <c r="E465">
         <v>1</v>
       </c>
@@ -13911,6 +14331,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D466">
+        <v>1</v>
+      </c>
       <c r="E466">
         <v>1</v>
       </c>
@@ -13940,6 +14363,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D467">
+        <v>1</v>
+      </c>
       <c r="E467">
         <v>1</v>
       </c>
@@ -13969,6 +14395,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D468">
+        <v>1</v>
+      </c>
       <c r="E468">
         <v>1</v>
       </c>
@@ -13998,6 +14427,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D469">
+        <v>4</v>
+      </c>
       <c r="E469">
         <v>2</v>
       </c>
@@ -14027,6 +14459,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D470">
+        <v>1</v>
+      </c>
       <c r="E470">
         <v>1</v>
       </c>
@@ -14056,6 +14491,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D471">
+        <v>1</v>
+      </c>
       <c r="E471">
         <v>1</v>
       </c>
@@ -14085,6 +14523,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D472">
+        <v>1</v>
+      </c>
       <c r="E472">
         <v>1</v>
       </c>
@@ -14114,6 +14555,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D473">
+        <v>1</v>
+      </c>
       <c r="E473">
         <v>2</v>
       </c>
@@ -14143,6 +14587,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D474">
+        <v>4</v>
+      </c>
       <c r="E474">
         <v>2</v>
       </c>
@@ -14172,6 +14619,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D475">
+        <v>1</v>
+      </c>
       <c r="E475">
         <v>1</v>
       </c>
@@ -14201,6 +14651,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D476">
+        <v>1</v>
+      </c>
       <c r="E476">
         <v>2</v>
       </c>
@@ -14230,6 +14683,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D477">
+        <v>1</v>
+      </c>
       <c r="E477">
         <v>2</v>
       </c>
@@ -14259,6 +14715,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D478">
+        <v>1</v>
+      </c>
       <c r="E478">
         <v>1</v>
       </c>
@@ -14288,6 +14747,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D479">
+        <v>1</v>
+      </c>
       <c r="E479">
         <v>1</v>
       </c>
@@ -14317,6 +14779,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D480">
+        <v>1</v>
+      </c>
       <c r="E480">
         <v>1</v>
       </c>
@@ -14346,6 +14811,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D481">
+        <v>1</v>
+      </c>
       <c r="E481">
         <v>1</v>
       </c>
@@ -14375,6 +14843,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D482">
+        <v>1</v>
+      </c>
       <c r="E482">
         <v>2</v>
       </c>
@@ -14404,6 +14875,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D483">
+        <v>4</v>
+      </c>
       <c r="E483">
         <v>2</v>
       </c>
@@ -14433,6 +14907,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D484">
+        <v>4</v>
+      </c>
       <c r="E484">
         <v>2</v>
       </c>
@@ -14462,6 +14939,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D485">
+        <v>1</v>
+      </c>
       <c r="E485">
         <v>1</v>
       </c>
@@ -14491,6 +14971,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D486">
+        <v>4</v>
+      </c>
       <c r="E486">
         <v>4</v>
       </c>
@@ -14520,6 +15003,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D487">
+        <v>1</v>
+      </c>
       <c r="E487">
         <v>1</v>
       </c>
@@ -14549,6 +15035,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D488">
+        <v>4</v>
+      </c>
       <c r="E488">
         <v>2</v>
       </c>
@@ -14578,6 +15067,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D489">
+        <v>4</v>
+      </c>
       <c r="E489">
         <v>2</v>
       </c>
@@ -14607,6 +15099,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D490">
+        <v>4</v>
+      </c>
       <c r="E490">
         <v>2</v>
       </c>
@@ -14636,6 +15131,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D491">
+        <v>4</v>
+      </c>
       <c r="E491">
         <v>2</v>
       </c>
@@ -14665,6 +15163,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D492">
+        <v>1</v>
+      </c>
       <c r="E492">
         <v>1</v>
       </c>
@@ -14694,6 +15195,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D493">
+        <v>4</v>
+      </c>
       <c r="E493">
         <v>2</v>
       </c>
@@ -14723,6 +15227,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D494">
+        <v>4</v>
+      </c>
       <c r="E494">
         <v>2</v>
       </c>
@@ -14752,6 +15259,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D495">
+        <v>1</v>
+      </c>
       <c r="E495">
         <v>1</v>
       </c>
@@ -14781,6 +15291,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D496">
+        <v>1</v>
+      </c>
       <c r="E496">
         <v>1</v>
       </c>
@@ -14810,6 +15323,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D497">
+        <v>1</v>
+      </c>
       <c r="E497">
         <v>1</v>
       </c>
@@ -14839,6 +15355,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D498">
+        <v>1</v>
+      </c>
       <c r="E498">
         <v>1</v>
       </c>
@@ -14868,6 +15387,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D499">
+        <v>1</v>
+      </c>
       <c r="E499">
         <v>1</v>
       </c>
@@ -14897,6 +15419,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D500">
+        <v>1</v>
+      </c>
       <c r="E500">
         <v>1</v>
       </c>
@@ -14926,6 +15451,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D501">
+        <v>1</v>
+      </c>
       <c r="E501">
         <v>1</v>
       </c>
@@ -14955,6 +15483,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D502">
+        <v>1</v>
+      </c>
       <c r="E502">
         <v>1</v>
       </c>
@@ -14984,6 +15515,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D503">
+        <v>1</v>
+      </c>
       <c r="E503">
         <v>1</v>
       </c>
@@ -15013,6 +15547,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D504">
+        <v>1</v>
+      </c>
       <c r="E504">
         <v>1</v>
       </c>
@@ -15042,6 +15579,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D505">
+        <v>1</v>
+      </c>
       <c r="E505">
         <v>1</v>
       </c>
@@ -15071,6 +15611,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D506">
+        <v>1</v>
+      </c>
       <c r="E506">
         <v>1</v>
       </c>
@@ -15129,6 +15672,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D508">
+        <v>1</v>
+      </c>
       <c r="E508">
         <v>1</v>
       </c>
@@ -15158,6 +15704,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D509">
+        <v>1</v>
+      </c>
       <c r="E509">
         <v>2</v>
       </c>
@@ -15187,6 +15736,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D510">
+        <v>4</v>
+      </c>
       <c r="E510">
         <v>1</v>
       </c>
@@ -15216,6 +15768,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D511">
+        <v>4</v>
+      </c>
       <c r="E511">
         <v>1</v>
       </c>
@@ -15245,6 +15800,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D512">
+        <v>1</v>
+      </c>
       <c r="E512">
         <v>1</v>
       </c>
@@ -15274,6 +15832,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D513">
+        <v>1</v>
+      </c>
       <c r="E513">
         <v>1</v>
       </c>
@@ -15303,6 +15864,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D514">
+        <v>1</v>
+      </c>
       <c r="E514">
         <v>1</v>
       </c>
@@ -15332,6 +15896,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D515">
+        <v>4</v>
+      </c>
       <c r="E515">
         <v>1</v>
       </c>
@@ -15361,6 +15928,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D516">
+        <v>4</v>
+      </c>
       <c r="E516">
         <v>1</v>
       </c>
@@ -15390,6 +15960,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
       <c r="E517">
         <v>1</v>
       </c>
@@ -15419,6 +15992,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D518">
+        <v>1</v>
+      </c>
       <c r="E518">
         <v>1</v>
       </c>
@@ -15448,6 +16024,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D519">
+        <v>4</v>
+      </c>
       <c r="E519">
         <v>1</v>
       </c>
@@ -15477,6 +16056,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D520">
+        <v>1</v>
+      </c>
       <c r="E520">
         <v>1</v>
       </c>
@@ -15506,6 +16088,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D521">
+        <v>4</v>
+      </c>
       <c r="E521">
         <v>1</v>
       </c>
@@ -15535,6 +16120,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
       <c r="E522">
         <v>1</v>
       </c>
@@ -15564,6 +16152,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D523">
+        <v>4</v>
+      </c>
       <c r="E523">
         <v>1</v>
       </c>
@@ -15593,6 +16184,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D524">
+        <v>1</v>
+      </c>
       <c r="E524">
         <v>1</v>
       </c>
@@ -15622,6 +16216,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D525">
+        <v>1</v>
+      </c>
       <c r="E525">
         <v>1</v>
       </c>
@@ -15651,6 +16248,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D526">
+        <v>1</v>
+      </c>
       <c r="E526">
         <v>1</v>
       </c>
@@ -15680,6 +16280,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D527">
+        <v>4</v>
+      </c>
       <c r="E527">
         <v>1</v>
       </c>
@@ -15709,6 +16312,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D528">
+        <v>4</v>
+      </c>
       <c r="E528">
         <v>1</v>
       </c>
@@ -15738,6 +16344,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D529">
+        <v>4</v>
+      </c>
       <c r="E529">
         <v>3</v>
       </c>
@@ -15767,6 +16376,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D530">
+        <v>4</v>
+      </c>
       <c r="E530">
         <v>1</v>
       </c>
@@ -15796,6 +16408,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D531">
+        <v>4</v>
+      </c>
       <c r="E531">
         <v>1</v>
       </c>
@@ -15825,6 +16440,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D532">
+        <v>4</v>
+      </c>
       <c r="E532">
         <v>2</v>
       </c>
@@ -15854,6 +16472,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D533">
+        <v>4</v>
+      </c>
       <c r="E533">
         <v>1</v>
       </c>
@@ -15883,6 +16504,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D534">
+        <v>4</v>
+      </c>
       <c r="E534">
         <v>1</v>
       </c>
@@ -15912,6 +16536,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D535">
+        <v>4</v>
+      </c>
       <c r="E535">
         <v>1</v>
       </c>
@@ -15941,6 +16568,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D536">
+        <v>1</v>
+      </c>
       <c r="E536">
         <v>1</v>
       </c>
@@ -15970,6 +16600,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D537">
+        <v>1</v>
+      </c>
       <c r="E537">
         <v>1</v>
       </c>
@@ -15999,6 +16632,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D538">
+        <v>1</v>
+      </c>
       <c r="E538">
         <v>1</v>
       </c>
@@ -16028,6 +16664,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D539">
+        <v>1</v>
+      </c>
       <c r="E539">
         <v>1</v>
       </c>
@@ -16057,6 +16696,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D540">
+        <v>1</v>
+      </c>
       <c r="E540">
         <v>1</v>
       </c>
@@ -16086,6 +16728,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D541">
+        <v>4</v>
+      </c>
       <c r="E541">
         <v>2</v>
       </c>
@@ -16115,6 +16760,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D542">
+        <v>1</v>
+      </c>
       <c r="E542">
         <v>1</v>
       </c>
@@ -16144,6 +16792,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D543">
+        <v>1</v>
+      </c>
       <c r="E543">
         <v>1</v>
       </c>
@@ -16173,6 +16824,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D544">
+        <v>4</v>
+      </c>
       <c r="E544">
         <v>2</v>
       </c>
@@ -16202,6 +16856,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D545">
+        <v>1</v>
+      </c>
       <c r="E545">
         <v>2</v>
       </c>
@@ -16231,6 +16888,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D546">
+        <v>1</v>
+      </c>
       <c r="E546">
         <v>2</v>
       </c>
@@ -16260,6 +16920,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D547">
+        <v>1</v>
+      </c>
       <c r="E547">
         <v>1</v>
       </c>
@@ -16289,6 +16952,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D548">
+        <v>1</v>
+      </c>
       <c r="E548">
         <v>1</v>
       </c>
@@ -16318,6 +16984,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D549">
+        <v>1</v>
+      </c>
       <c r="E549">
         <v>2</v>
       </c>
@@ -16347,6 +17016,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D550">
+        <v>4</v>
+      </c>
       <c r="E550">
         <v>2</v>
       </c>
@@ -16376,6 +17048,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D551">
+        <v>4</v>
+      </c>
       <c r="E551">
         <v>2</v>
       </c>
@@ -16405,6 +17080,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D552">
+        <v>1</v>
+      </c>
       <c r="E552">
         <v>1</v>
       </c>
@@ -16434,6 +17112,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D553">
+        <v>1</v>
+      </c>
       <c r="E553">
         <v>1</v>
       </c>
@@ -16463,6 +17144,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D554">
+        <v>1</v>
+      </c>
       <c r="E554">
         <v>2</v>
       </c>
@@ -16492,6 +17176,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D555">
+        <v>1</v>
+      </c>
       <c r="E555">
         <v>2</v>
       </c>
@@ -16521,6 +17208,9 @@
           <t>microsiemens per centimetre</t>
         </is>
       </c>
+      <c r="D556">
+        <v>4</v>
+      </c>
       <c r="E556">
         <v>2</v>
       </c>
@@ -16550,6 +17240,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D557">
+        <v>1</v>
+      </c>
       <c r="E557">
         <v>2</v>
       </c>
@@ -16579,6 +17272,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D558">
+        <v>1</v>
+      </c>
       <c r="E558">
         <v>1</v>
       </c>
@@ -16608,6 +17304,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D559">
+        <v>1</v>
+      </c>
       <c r="E559">
         <v>1</v>
       </c>
@@ -16637,6 +17336,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D560">
+        <v>1</v>
+      </c>
       <c r="E560">
         <v>1</v>
       </c>
@@ -16666,6 +17368,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D561">
+        <v>1</v>
+      </c>
       <c r="E561">
         <v>1</v>
       </c>
@@ -16695,6 +17400,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D562">
+        <v>1</v>
+      </c>
       <c r="E562">
         <v>1</v>
       </c>
@@ -16724,6 +17432,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D563">
+        <v>1</v>
+      </c>
       <c r="E563">
         <v>1</v>
       </c>
@@ -16753,6 +17464,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
       <c r="E564">
         <v>1</v>
       </c>
@@ -16782,6 +17496,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D565">
+        <v>1</v>
+      </c>
       <c r="E565">
         <v>1</v>
       </c>
@@ -16811,6 +17528,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D566">
+        <v>1</v>
+      </c>
       <c r="E566">
         <v>1</v>
       </c>
@@ -16840,6 +17560,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D567">
+        <v>4</v>
+      </c>
       <c r="E567">
         <v>2</v>
       </c>
@@ -16869,6 +17592,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D568">
+        <v>1</v>
+      </c>
       <c r="E568">
         <v>1</v>
       </c>
@@ -16898,6 +17624,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D569">
+        <v>1</v>
+      </c>
       <c r="E569">
         <v>1</v>
       </c>
@@ -16927,6 +17656,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D570">
+        <v>1</v>
+      </c>
       <c r="E570">
         <v>1</v>
       </c>
@@ -16956,6 +17688,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D571">
+        <v>1</v>
+      </c>
       <c r="E571">
         <v>2</v>
       </c>
@@ -16985,6 +17720,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D572">
+        <v>4</v>
+      </c>
       <c r="E572">
         <v>2</v>
       </c>
@@ -17014,6 +17752,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D573">
+        <v>1</v>
+      </c>
       <c r="E573">
         <v>1</v>
       </c>
@@ -17043,6 +17784,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D574">
+        <v>1</v>
+      </c>
       <c r="E574">
         <v>2</v>
       </c>
@@ -17072,6 +17816,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D575">
+        <v>1</v>
+      </c>
       <c r="E575">
         <v>2</v>
       </c>
@@ -17101,6 +17848,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D576">
+        <v>1</v>
+      </c>
       <c r="E576">
         <v>1</v>
       </c>
@@ -17130,6 +17880,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D577">
+        <v>1</v>
+      </c>
       <c r="E577">
         <v>1</v>
       </c>
@@ -17159,6 +17912,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D578">
+        <v>1</v>
+      </c>
       <c r="E578">
         <v>1</v>
       </c>
@@ -17188,6 +17944,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D579">
+        <v>1</v>
+      </c>
       <c r="E579">
         <v>1</v>
       </c>
@@ -17217,6 +17976,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D580">
+        <v>1</v>
+      </c>
       <c r="E580">
         <v>2</v>
       </c>
@@ -17246,6 +18008,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D581">
+        <v>4</v>
+      </c>
       <c r="E581">
         <v>2</v>
       </c>
@@ -17275,6 +18040,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D582">
+        <v>4</v>
+      </c>
       <c r="E582">
         <v>2</v>
       </c>
@@ -17304,6 +18072,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D583">
+        <v>1</v>
+      </c>
       <c r="E583">
         <v>1</v>
       </c>
@@ -17333,6 +18104,9 @@
           <t>pH units</t>
         </is>
       </c>
+      <c r="D584">
+        <v>4</v>
+      </c>
       <c r="E584">
         <v>4</v>
       </c>
@@ -17362,6 +18136,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D585">
+        <v>1</v>
+      </c>
       <c r="E585">
         <v>1</v>
       </c>
@@ -17391,6 +18168,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D586">
+        <v>4</v>
+      </c>
       <c r="E586">
         <v>2</v>
       </c>
@@ -17420,6 +18200,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D587">
+        <v>4</v>
+      </c>
       <c r="E587">
         <v>2</v>
       </c>
@@ -17449,6 +18232,9 @@
           <t>metres</t>
         </is>
       </c>
+      <c r="D588">
+        <v>4</v>
+      </c>
       <c r="E588">
         <v>2</v>
       </c>
@@ -17478,6 +18264,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D589">
+        <v>4</v>
+      </c>
       <c r="E589">
         <v>2</v>
       </c>
@@ -17507,6 +18296,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D590">
+        <v>1</v>
+      </c>
       <c r="E590">
         <v>1</v>
       </c>
@@ -17536,6 +18328,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D591">
+        <v>4</v>
+      </c>
       <c r="E591">
         <v>2</v>
       </c>
@@ -17565,6 +18360,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D592">
+        <v>4</v>
+      </c>
       <c r="E592">
         <v>2</v>
       </c>
@@ -17594,6 +18392,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D593">
+        <v>1</v>
+      </c>
       <c r="E593">
         <v>1</v>
       </c>
@@ -17623,6 +18424,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D594">
+        <v>1</v>
+      </c>
       <c r="E594">
         <v>1</v>
       </c>
@@ -17652,6 +18456,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D595">
+        <v>1</v>
+      </c>
       <c r="E595">
         <v>1</v>
       </c>
@@ -17681,6 +18488,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D596">
+        <v>1</v>
+      </c>
       <c r="E596">
         <v>1</v>
       </c>
@@ -17710,6 +18520,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
       <c r="E597">
         <v>1</v>
       </c>
@@ -17739,6 +18552,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D598">
+        <v>1</v>
+      </c>
       <c r="E598">
         <v>1</v>
       </c>
@@ -17768,6 +18584,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D599">
+        <v>1</v>
+      </c>
       <c r="E599">
         <v>1</v>
       </c>
@@ -17797,6 +18616,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D600">
+        <v>1</v>
+      </c>
       <c r="E600">
         <v>1</v>
       </c>
@@ -17826,6 +18648,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D601">
+        <v>1</v>
+      </c>
       <c r="E601">
         <v>1</v>
       </c>
@@ -17855,6 +18680,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D602">
+        <v>1</v>
+      </c>
       <c r="E602">
         <v>1</v>
       </c>
@@ -17884,6 +18712,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D603">
+        <v>1</v>
+      </c>
       <c r="E603">
         <v>1</v>
       </c>
@@ -17913,6 +18744,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D604">
+        <v>1</v>
+      </c>
       <c r="E604">
         <v>1</v>
       </c>
@@ -17971,6 +18805,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D606">
+        <v>1</v>
+      </c>
       <c r="E606">
         <v>1</v>
       </c>
@@ -18000,6 +18837,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D607">
+        <v>1</v>
+      </c>
       <c r="E607">
         <v>2</v>
       </c>
@@ -18029,17 +18869,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D608">
+        <v>1</v>
+      </c>
       <c r="E608">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F608">
         <v>7</v>
       </c>
       <c r="G608">
-        <v>9</v>
+        <v>155.5</v>
       </c>
       <c r="H608">
-        <v>11</v>
+        <v>360</v>
       </c>
     </row>
     <row r="609">
@@ -18058,6 +18901,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D609">
+        <v>1</v>
+      </c>
       <c r="E609">
         <v>1</v>
       </c>
@@ -18087,17 +18933,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D610">
+        <v>1</v>
+      </c>
       <c r="E610">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F610">
         <v>0.06</v>
       </c>
       <c r="G610">
-        <v>0.095</v>
+        <v>9.53</v>
       </c>
       <c r="H610">
-        <v>0.13</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="611">
@@ -18116,8 +18965,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D611">
+        <v>1</v>
+      </c>
       <c r="E611">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F611" s="3">
         <v>0.001</v>
@@ -18145,17 +18997,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D612">
+        <v>1</v>
+      </c>
       <c r="E612">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F612">
         <v>0.043</v>
       </c>
       <c r="G612">
-        <v>0.0435</v>
+        <v>0.3185</v>
       </c>
       <c r="H612">
-        <v>0.044</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="613">
@@ -18174,6 +19029,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D613">
+        <v>1</v>
+      </c>
       <c r="E613">
         <v>1</v>
       </c>
@@ -18203,8 +19061,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D614">
+        <v>1</v>
+      </c>
       <c r="E614">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F614" s="3">
         <v>0.0001</v>
@@ -18232,17 +19093,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D615">
+        <v>1</v>
+      </c>
       <c r="E615">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F615">
         <v>3</v>
       </c>
       <c r="G615">
-        <v>4</v>
+        <v>30.5</v>
       </c>
       <c r="H615">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="616">
@@ -18261,17 +19125,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D616">
+        <v>1</v>
+      </c>
       <c r="E616">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F616">
         <v>4</v>
       </c>
       <c r="G616">
-        <v>5.5</v>
+        <v>29.25</v>
       </c>
       <c r="H616">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="617">
@@ -18290,6 +19157,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D617">
+        <v>1</v>
+      </c>
       <c r="E617">
         <v>1</v>
       </c>
@@ -18319,8 +19189,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D618">
+        <v>1</v>
+      </c>
       <c r="E618">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F618" s="3">
         <v>0.001</v>
@@ -18348,17 +19221,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D619">
+        <v>1</v>
+      </c>
       <c r="E619">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F619" s="3">
         <v>0.001</v>
       </c>
-      <c r="G619" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="H619" s="3">
-        <v>0.001</v>
+      <c r="G619">
+        <v>0.00125</v>
+      </c>
+      <c r="H619">
+        <v>0.002</v>
       </c>
     </row>
     <row r="620">
@@ -18378,16 +19254,16 @@
         </is>
       </c>
       <c r="E620">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F620">
         <v>34</v>
       </c>
       <c r="G620">
-        <v>37.5</v>
+        <v>373</v>
       </c>
       <c r="H620">
-        <v>41</v>
+        <v>887</v>
       </c>
     </row>
     <row r="621">
@@ -18406,8 +19282,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D621">
+        <v>1</v>
+      </c>
       <c r="E621">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F621">
         <v>0.001</v>
@@ -18435,6 +19314,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D622">
+        <v>1</v>
+      </c>
       <c r="E622">
         <v>1</v>
       </c>
@@ -18464,16 +19346,19 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D623">
+        <v>1</v>
+      </c>
       <c r="E623">
-        <v>2</v>
-      </c>
-      <c r="F623" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="G623" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="H623" s="3">
+        <v>4</v>
+      </c>
+      <c r="F623">
+        <v>0.1</v>
+      </c>
+      <c r="G623">
+        <v>0.1</v>
+      </c>
+      <c r="H623">
         <v>0.1</v>
       </c>
     </row>
@@ -18493,8 +19378,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D624">
+        <v>1</v>
+      </c>
       <c r="E624">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F624" s="3">
         <v>0.001</v>
@@ -18522,17 +19410,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D625">
+        <v>1</v>
+      </c>
       <c r="E625">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F625" s="3">
         <v>1</v>
       </c>
-      <c r="G625" s="3">
-        <v>1</v>
-      </c>
-      <c r="H625" s="3">
-        <v>1</v>
+      <c r="G625">
+        <v>4</v>
+      </c>
+      <c r="H625">
+        <v>7</v>
       </c>
     </row>
     <row r="626">
@@ -18551,17 +19442,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D626">
+        <v>1</v>
+      </c>
       <c r="E626">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F626">
         <v>0.009</v>
       </c>
       <c r="G626">
-        <v>0.0935</v>
+        <v>0.72575</v>
       </c>
       <c r="H626">
-        <v>0.178</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="627">
@@ -18580,8 +19474,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D627">
+        <v>1</v>
+      </c>
       <c r="E627">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F627" s="3">
         <v>0.0001</v>
@@ -18609,17 +19506,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D628">
+        <v>1</v>
+      </c>
       <c r="E628">
-        <v>2</v>
-      </c>
-      <c r="F628" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="G628" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="H628" s="3">
-        <v>0.001</v>
+        <v>4</v>
+      </c>
+      <c r="F628">
+        <v>0.001</v>
+      </c>
+      <c r="G628">
+        <v>0.00175</v>
+      </c>
+      <c r="H628">
+        <v>0.004</v>
       </c>
     </row>
     <row r="629">
@@ -18638,17 +19538,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D629">
+        <v>1</v>
+      </c>
       <c r="E629">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F629" s="3">
         <v>0.01</v>
       </c>
       <c r="G629">
-        <v>0.015</v>
+        <v>0.5125</v>
       </c>
       <c r="H629">
-        <v>0.02</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="630">
@@ -18667,17 +19570,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D630">
+        <v>1</v>
+      </c>
       <c r="E630">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F630" s="3">
         <v>0.01</v>
       </c>
-      <c r="G630" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H630" s="3">
-        <v>0.01</v>
+      <c r="G630">
+        <v>0.02</v>
+      </c>
+      <c r="H630">
+        <v>0.05</v>
       </c>
     </row>
     <row r="631">
@@ -18697,16 +19603,16 @@
         </is>
       </c>
       <c r="E631">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F631">
         <v>6.41</v>
       </c>
       <c r="G631">
-        <v>6.69</v>
+        <v>6.83428571428571</v>
       </c>
       <c r="H631">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="632">
@@ -18725,6 +19631,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D632">
+        <v>1</v>
+      </c>
       <c r="E632">
         <v>1</v>
       </c>
@@ -18754,17 +19663,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D633">
+        <v>1</v>
+      </c>
       <c r="E633">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F633">
         <v>1</v>
       </c>
       <c r="G633">
-        <v>1</v>
+        <v>15.75</v>
       </c>
       <c r="H633">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="634">
@@ -18783,17 +19695,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D634">
+        <v>1</v>
+      </c>
       <c r="E634">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F634">
         <v>1</v>
       </c>
       <c r="G634">
-        <v>1.5</v>
+        <v>19.25</v>
       </c>
       <c r="H634">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="635">
@@ -18812,17 +19727,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D635">
+        <v>1</v>
+      </c>
       <c r="E635">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F635" s="3">
         <v>1</v>
       </c>
       <c r="G635">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="H635">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="636">
@@ -18841,6 +19759,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D636">
+        <v>1</v>
+      </c>
       <c r="E636">
         <v>1</v>
       </c>
@@ -18870,17 +19791,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D637">
+        <v>1</v>
+      </c>
       <c r="E637">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F637">
         <v>22</v>
       </c>
       <c r="G637">
-        <v>24.5</v>
+        <v>242.25</v>
       </c>
       <c r="H637">
-        <v>27</v>
+        <v>576</v>
       </c>
     </row>
     <row r="638">
@@ -18899,17 +19823,20 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D638">
+        <v>1</v>
+      </c>
       <c r="E638">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F638">
         <v>7</v>
       </c>
       <c r="G638">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
       <c r="H638">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="639">
@@ -18928,6 +19855,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D639">
+        <v>1</v>
+      </c>
       <c r="E639">
         <v>1</v>
       </c>
@@ -18957,6 +19887,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D640">
+        <v>1</v>
+      </c>
       <c r="E640">
         <v>1</v>
       </c>
@@ -18986,6 +19919,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D641">
+        <v>1</v>
+      </c>
       <c r="E641">
         <v>1</v>
       </c>
@@ -19015,6 +19951,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D642">
+        <v>1</v>
+      </c>
       <c r="E642">
         <v>1</v>
       </c>
@@ -19044,6 +19983,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D643">
+        <v>1</v>
+      </c>
       <c r="E643">
         <v>1</v>
       </c>
@@ -19073,6 +20015,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D644">
+        <v>1</v>
+      </c>
       <c r="E644">
         <v>1</v>
       </c>
@@ -19102,6 +20047,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D645">
+        <v>1</v>
+      </c>
       <c r="E645">
         <v>1</v>
       </c>
@@ -19131,6 +20079,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D646">
+        <v>1</v>
+      </c>
       <c r="E646">
         <v>1</v>
       </c>
@@ -19160,6 +20111,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D647">
+        <v>1</v>
+      </c>
       <c r="E647">
         <v>1</v>
       </c>
@@ -19189,6 +20143,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D648">
+        <v>1</v>
+      </c>
       <c r="E648">
         <v>1</v>
       </c>
@@ -19218,6 +20175,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D649">
+        <v>1</v>
+      </c>
       <c r="E649">
         <v>1</v>
       </c>
@@ -19247,6 +20207,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D650">
+        <v>1</v>
+      </c>
       <c r="E650">
         <v>1</v>
       </c>
@@ -19276,6 +20239,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D651">
+        <v>1</v>
+      </c>
       <c r="E651">
         <v>1</v>
       </c>
@@ -19305,6 +20271,9 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D652">
+        <v>1</v>
+      </c>
       <c r="E652">
         <v>1</v>
       </c>
@@ -19334,8 +20303,11 @@
           <t>milligrams per litre</t>
         </is>
       </c>
+      <c r="D653">
+        <v>1</v>
+      </c>
       <c r="E653">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F653" s="3">
         <v>0.005</v>
@@ -19358,6 +20330,20 @@
       <c r="A656" s="3" t="inlineStr">
         <is>
           <t>A Lowest or Highest value in grey italics was attained only by below-detection results. A Mean in grey italics indicates that every result for that monitoring point and pollutant was below detection. Figures in normal type are measured values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="3" t="inlineStr">
+        <is>
+          <t>No. of samples required is taken from licence conditions M2.2 and M2.3 (Quarterly = 4, Yearly = 1). It is left blank where the licence sets no requirement for that pollutant at that point, and for points 2 and 3, where condition M2.4(a) Special Frequency 1 requires sampling within the first 24 hours of each discharge rather than a fixed number of samples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="3" t="inlineStr">
+        <is>
+          <t>At point 1 the number of samples collected counts individual grid locations. The quarterly requirement refers to monitoring events.</t>
         </is>
       </c>
     </row>
